--- a/public/_fixtures/plan-full.xlsx
+++ b/public/_fixtures/plan-full.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="83">
   <si>
     <t>عنوان</t>
   </si>
@@ -74,6 +74,18 @@
     <t>بطولة الدولة</t>
   </si>
   <si>
+    <t>إجراءات الاستشفاء</t>
+  </si>
+  <si>
+    <t>تهدئة ونوم وترطيب</t>
+  </si>
+  <si>
+    <t>إجراءات السلامة والوقاية</t>
+  </si>
+  <si>
+    <t>فحص البساط وتدرّج الأوكيمي</t>
+  </si>
+  <si>
     <t>م</t>
   </si>
   <si>
@@ -164,18 +176,27 @@
     <t>الراحة (د)</t>
   </si>
   <si>
+    <t>نوع المحتوى</t>
+  </si>
+  <si>
     <t>الأحد</t>
   </si>
   <si>
     <t>2026-09-01</t>
   </si>
   <si>
+    <t>هدف</t>
+  </si>
+  <si>
     <t>الإحماء</t>
   </si>
   <si>
     <t>حركية</t>
   </si>
   <si>
+    <t>بدني</t>
+  </si>
+  <si>
     <t>الجزء الرئيسي</t>
   </si>
   <si>
@@ -185,12 +206,18 @@
     <t>4×10</t>
   </si>
   <si>
+    <t>فني</t>
+  </si>
+  <si>
     <t>التهدئة</t>
   </si>
   <si>
     <t>تمطيط</t>
   </si>
   <si>
+    <t>نفسي</t>
+  </si>
+  <si>
     <t>2026-09-02</t>
   </si>
   <si>
@@ -200,6 +227,9 @@
     <t>2026-09-04</t>
   </si>
   <si>
+    <t>خططي</t>
+  </si>
+  <si>
     <t>المؤشر أو الاختبار</t>
   </si>
   <si>
@@ -222,6 +252,18 @@
   </si>
   <si>
     <t>عدّ يدوي</t>
+  </si>
+  <si>
+    <t>زمن 5 دقائق راندوري</t>
+  </si>
+  <si>
+    <t>3 نقاط</t>
+  </si>
+  <si>
+    <t>5 نقاط</t>
+  </si>
+  <si>
+    <t>تصوير</t>
   </si>
 </sst>
 </file>
@@ -598,7 +640,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -676,6 +718,22 @@
       </c>
       <c r="B11" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -696,30 +754,30 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -727,13 +785,13 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -754,16 +812,16 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -771,13 +829,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -785,13 +843,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -799,13 +857,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -813,13 +871,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D7" t="s">
         <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -830,7 +888,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -838,62 +896,65 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C3" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F3" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H3" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="I3" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="K3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D4" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E4" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F4">
         <v>18</v>
       </c>
       <c r="G4" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I4">
         <v>3</v>
@@ -901,31 +962,34 @@
       <c r="J4">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F5">
         <v>67</v>
       </c>
       <c r="G5" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="H5" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I5">
         <v>7</v>
@@ -933,31 +997,34 @@
       <c r="J5">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E6" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F6">
         <v>10</v>
       </c>
       <c r="G6" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I6">
         <v>2</v>
@@ -965,31 +1032,34 @@
       <c r="J6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F7">
         <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I7">
         <v>3</v>
@@ -997,31 +1067,34 @@
       <c r="J7">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F8">
         <v>67</v>
       </c>
       <c r="G8" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="H8" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I8">
         <v>8</v>
@@ -1029,31 +1102,34 @@
       <c r="J8">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>2</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F9">
         <v>10</v>
       </c>
       <c r="G9" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -1061,31 +1137,34 @@
       <c r="J9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>3</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C10" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E10" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F10">
         <v>18</v>
       </c>
       <c r="G10" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H10" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I10">
         <v>3</v>
@@ -1093,31 +1172,34 @@
       <c r="J10">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E11" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F11">
         <v>67</v>
       </c>
       <c r="G11" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="H11" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I11">
         <v>6</v>
@@ -1125,31 +1207,34 @@
       <c r="J11">
         <v>2</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F12">
         <v>10</v>
       </c>
       <c r="G12" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H12" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I12">
         <v>2</v>
@@ -1157,31 +1242,34 @@
       <c r="J12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F13">
         <v>18</v>
       </c>
       <c r="G13" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="H13" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I13">
         <v>3</v>
@@ -1189,31 +1277,34 @@
       <c r="J13">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K13" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
         <v>60</v>
-      </c>
-      <c r="D14" t="s">
-        <v>42</v>
-      </c>
-      <c r="E14" t="s">
-        <v>53</v>
       </c>
       <c r="F14">
         <v>67</v>
       </c>
       <c r="G14" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="H14" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="I14">
         <v>9</v>
@@ -1221,37 +1312,43 @@
       <c r="J14">
         <v>2</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>4</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="F15">
         <v>10</v>
       </c>
       <c r="G15" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H15" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="I15">
         <v>2</v>
       </c>
       <c r="J15">
         <v>0</v>
+      </c>
+      <c r="K15" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -1262,7 +1359,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
@@ -1272,19 +1369,19 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="E3" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -1292,16 +1389,33 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>68</v>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
